--- a/jira_export_2026-07-15.xlsx
+++ b/jira_export_2026-07-15.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>22,554 €</t>
+          <t>22,948 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>16,537 €</t>
+          <t>16,931 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>318 h</t>
+          <t>321 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -895,7 +895,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:P175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4549,8 +4549,8 @@
       <c r="N53" s="13" t="n">
         <v>149</v>
       </c>
-      <c r="O53" s="17" t="n">
-        <v>0</v>
+      <c r="O53" s="13" t="n">
+        <v>149</v>
       </c>
       <c r="P53" s="13" t="n">
         <v>0</v>
@@ -5135,27 +5135,27 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32869</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00164607</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O62" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>245</v>
       </c>
       <c r="P62" s="16" t="n">
         <v>0</v>
@@ -5207,12 +5207,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
@@ -5258,16 +5258,16 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="O63" s="17" t="n">
         <v>0</v>
@@ -5279,32 +5279,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5319,27 +5319,27 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="O64" s="17" t="n">
         <v>0</v>
@@ -5351,12 +5351,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
@@ -5398,20 +5398,20 @@
         <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>564</v>
+        <v>705</v>
       </c>
       <c r="O65" s="17" t="n">
         <v>0</v>
@@ -5423,32 +5423,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
@@ -5470,37 +5470,37 @@
         <v>3</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>2138.2</v>
+        <v>564</v>
       </c>
       <c r="O66" s="17" t="n">
-        <v>1375.2</v>
+        <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>305.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5530,69 +5530,69 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>283.5</v>
+        <v>2138.2</v>
       </c>
       <c r="O67" s="17" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>0</v>
+        <v>305.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>548.4</v>
+        <v>283.5</v>
       </c>
       <c r="O68" s="17" t="n">
         <v>0</v>
@@ -5639,32 +5639,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
@@ -5686,20 +5686,20 @@
         <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>552</v>
+        <v>548.4</v>
       </c>
       <c r="O69" s="17" t="n">
         <v>0</v>
@@ -5711,32 +5711,32 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5746,32 +5746,32 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>142.1</v>
+        <v>552</v>
       </c>
       <c r="O70" s="17" t="n">
         <v>0</v>
@@ -5783,32 +5783,32 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>1868</v>
+        <v>142.1</v>
       </c>
       <c r="O71" s="17" t="n">
         <v>0</v>
@@ -5855,32 +5855,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5890,32 +5890,32 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>882.5</v>
+        <v>1868</v>
       </c>
       <c r="O72" s="17" t="n">
         <v>0</v>
@@ -5927,27 +5927,27 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5967,29 +5967,29 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="13" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="O73" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="13" t="n">
@@ -5999,32 +5999,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6034,35 +6034,35 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
         <v>0</v>
@@ -6071,32 +6071,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6106,69 +6106,69 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O75" s="17" t="n">
-        <v>637</v>
+        <v>450</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>450</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>74.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6178,64 +6178,64 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>3.25</v>
+        <v>8.5</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>765</v>
+        <v>1046.5</v>
       </c>
       <c r="O76" s="17" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6262,52 +6262,52 @@
         <v>4</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>1</v>
+        <v>3.25</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13" t="n">
-        <v>100</v>
+        <v>765</v>
+      </c>
+      <c r="O77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6322,49 +6322,49 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>407</v>
-      </c>
-      <c r="O78" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>100</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6394,32 +6394,32 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>257.15</v>
+        <v>407</v>
       </c>
       <c r="O79" s="17" t="n">
         <v>0</v>
@@ -6431,32 +6431,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>440.38</v>
+        <v>257.15</v>
       </c>
       <c r="O80" s="17" t="n">
         <v>0</v>
@@ -6503,32 +6503,32 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
@@ -6554,16 +6554,16 @@
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>285</v>
+        <v>440.38</v>
       </c>
       <c r="O81" s="17" t="n">
         <v>0</v>
@@ -6575,32 +6575,32 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6626,19 +6626,19 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>120</v>
+        <v>285</v>
+      </c>
+      <c r="O82" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
         <v>0</v>
@@ -6647,32 +6647,32 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6698,19 +6698,19 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="O83" s="17" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>120</v>
       </c>
       <c r="P83" s="13" t="n">
         <v>0</v>
@@ -6719,27 +6719,27 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -6770,19 +6770,19 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="16" t="n">
-        <v>367.5</v>
+        <v>45</v>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
         <v>0</v>
@@ -6791,12 +6791,12 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6831,30 +6831,30 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="O85" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>367.5</v>
       </c>
       <c r="P85" s="13" t="n">
         <v>0</v>
@@ -6863,27 +6863,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6898,32 +6898,32 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>203.5</v>
+        <v>420</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6935,12 +6935,12 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6970,34 +6970,34 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="13" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O87" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
@@ -7007,32 +7007,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7042,64 +7042,64 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O88" s="17" t="n">
-        <v>214.9</v>
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>143.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -7126,82 +7126,82 @@
         <v>5</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L89" s="12" t="inlineStr"/>
-      <c r="M89" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="13" t="n">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="O89" s="17" t="n">
+        <v>214.9</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>0</v>
+        <v>143.27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L90" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31488</t>
-        </is>
-      </c>
-      <c r="M90" s="15" t="inlineStr">
-        <is>
-          <t>00157472</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L90" s="15" t="inlineStr"/>
+      <c r="M90" s="15" t="inlineStr"/>
       <c r="N90" s="16" t="n">
         <v>0</v>
       </c>
@@ -7215,32 +7215,32 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7250,28 +7250,28 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
@@ -7287,32 +7287,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7322,34 +7322,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7359,27 +7359,27 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
@@ -7406,22 +7406,22 @@
         <v>5</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>210</v>
+      </c>
+      <c r="O93" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7431,32 +7431,32 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7471,29 +7471,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7503,27 +7503,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7543,29 +7543,29 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="O95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7575,32 +7575,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7610,34 +7610,34 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="O96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7647,12 +7647,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
@@ -7698,16 +7698,16 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O97" s="17" t="n">
         <v>0</v>
@@ -7719,12 +7719,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7759,27 +7759,27 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="O98" s="17" t="n">
         <v>0</v>
@@ -7791,12 +7791,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
@@ -7842,16 +7842,16 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="O99" s="17" t="n">
         <v>0</v>
@@ -7863,27 +7863,27 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
@@ -7914,16 +7914,16 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -7935,32 +7935,32 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7970,34 +7970,34 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="O101" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -8007,12 +8007,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
@@ -8058,18 +8058,18 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="O102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8079,27 +8079,27 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -8119,29 +8119,29 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>6.25</v>
+        <v>0.75</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="O103" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8151,32 +8151,32 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8186,28 +8186,28 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
@@ -8223,32 +8223,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8258,28 +8258,28 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8439,32 +8439,32 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
@@ -8474,28 +8474,28 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8511,30 +8511,32 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v/>
+          <t>Commune de Calais</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -8544,34 +8546,34 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8581,32 +8583,30 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v/>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8616,34 +8616,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O110" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
@@ -8716,39 +8716,41 @@
         <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8758,12 +8760,12 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
@@ -8774,33 +8776,33 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O112" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O112" s="16" t="n">
+        <v>405</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8810,13 +8812,11 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8835,27 +8835,27 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O113" s="17" t="n">
         <v>0</v>
@@ -8918,16 +8918,16 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O114" s="17" t="n">
         <v>0</v>
@@ -8990,16 +8990,16 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O115" s="17" t="n">
         <v>0</v>
@@ -9062,18 +9062,18 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O116" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9155,12 +9155,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9170,11 +9170,13 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9188,28 +9190,28 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>4.25</v>
+        <v>1.15</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9225,12 +9227,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9240,7 +9242,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9258,34 +9260,34 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>732</v>
-      </c>
-      <c r="O119" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="13" t="n">
@@ -9295,12 +9297,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9310,38 +9312,52 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="inlineStr"/>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F120" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr"/>
-      <c r="M120" s="15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>732</v>
+      </c>
+      <c r="O120" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9351,12 +9367,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9366,83 +9382,67 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v/>
-      </c>
-      <c r="F121" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr"/>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr"/>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L121" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M121" s="12" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L121" s="12" t="inlineStr"/>
+      <c r="M121" s="12" t="inlineStr"/>
       <c r="N121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O121" s="13" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v/>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
@@ -9456,63 +9456,65 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>9.25</v>
+        <v>1.25</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O122" s="16" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
@@ -9531,29 +9533,29 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>1.5</v>
+        <v>9.25</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9563,12 +9565,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9578,7 +9580,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9596,34 +9598,34 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O124" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9633,22 +9635,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9671,23 +9673,23 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9703,12 +9705,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9718,7 +9720,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9736,28 +9738,28 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9822,12 +9824,12 @@
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9843,22 +9845,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9881,29 +9883,29 @@
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9913,22 +9915,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9936,7 +9938,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -9946,32 +9948,32 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>964.1</v>
+        <v>2323</v>
       </c>
       <c r="O129" s="17" t="n">
         <v>0</v>
@@ -9983,12 +9985,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -10032,19 +10034,19 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="O130" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
         <v>0</v>
@@ -10053,22 +10055,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10076,7 +10078,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -10086,35 +10088,35 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="13" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O131" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P131" s="13" t="n">
         <v>0</v>
@@ -10123,22 +10125,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10156,28 +10158,28 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10193,22 +10195,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10226,28 +10228,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10312,12 +10314,12 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10348,7 +10350,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10382,12 +10384,12 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10418,7 +10420,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10452,12 +10454,12 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10473,12 +10475,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10488,7 +10490,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10506,28 +10508,28 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10543,22 +10545,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10581,23 +10583,23 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K138" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10613,22 +10615,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10636,7 +10638,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10651,29 +10653,29 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O139" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="13" t="n">
@@ -10683,18 +10685,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr"/>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10702,7 +10708,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10728,19 +10734,19 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="16" t="n">
-        <v>575</v>
+        <v>482.72</v>
+      </c>
+      <c r="O140" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
         <v>0</v>
@@ -10749,22 +10755,18 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr"/>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10782,35 +10784,35 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="13" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10819,22 +10821,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10852,34 +10854,34 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
@@ -10889,22 +10891,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10927,27 +10929,27 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O143" s="17" t="n">
         <v>0</v>
@@ -10959,22 +10961,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10990,24 +10992,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H144" s="15" t="inlineStr"/>
+      <c r="H144" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr"/>
-      <c r="M144" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M144" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N144" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O144" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
@@ -11017,22 +11031,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11048,32 +11062,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H145" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H145" s="12" t="inlineStr"/>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11087,12 +11089,12 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
@@ -11102,7 +11104,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11120,28 +11122,28 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11157,12 +11159,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11172,7 +11174,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11190,28 +11192,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11227,12 +11229,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11242,7 +11244,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11265,23 +11267,23 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11297,22 +11299,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11325,27 +11327,35 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L149" s="12" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L149" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N149" s="13" t="n">
         <v>0</v>
       </c>
@@ -11359,22 +11369,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11392,7 +11402,7 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
@@ -11404,7 +11414,7 @@
         <v>19</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>4.5</v>
+        <v>0.75</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11421,22 +11431,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11444,7 +11454,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -11466,7 +11476,7 @@
         <v>19</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11483,12 +11493,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11498,7 +11508,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11511,39 +11521,31 @@
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M152" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr"/>
+      <c r="M152" s="15" t="inlineStr"/>
       <c r="N152" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="16" t="n">
@@ -11553,22 +11555,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11576,7 +11578,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -11586,34 +11588,34 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O153" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11638,7 +11640,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11672,7 +11674,7 @@
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
@@ -11693,22 +11695,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11716,32 +11718,40 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr"/>
-      <c r="M155" s="12" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
@@ -11755,22 +11765,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11778,7 +11788,7 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
@@ -11788,19 +11798,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>0.25</v>
+        <v>4.25</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11817,22 +11827,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11855,14 +11865,14 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11879,22 +11889,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11907,7 +11917,7 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
@@ -11917,17 +11927,25 @@
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr"/>
-      <c r="M158" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M158" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N158" s="16" t="n">
         <v>0</v>
       </c>
@@ -11941,12 +11959,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -11956,7 +11974,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11979,14 +11997,14 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -12003,12 +12021,12 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
@@ -12018,7 +12036,7 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12036,19 +12054,19 @@
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>7.25</v>
+        <v>1.5</v>
       </c>
       <c r="L160" s="15" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -12065,12 +12083,12 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
@@ -12080,7 +12098,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12093,7 +12111,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -12103,25 +12121,17 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M161" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr"/>
+      <c r="M161" s="12" t="inlineStr"/>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
@@ -12135,12 +12145,12 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
@@ -12150,7 +12160,7 @@
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12163,20 +12173,24 @@
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H162" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H162" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12193,22 +12207,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12221,31 +12235,35 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M163" s="12" t="inlineStr"/>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N163" s="13" t="n">
         <v>0</v>
       </c>
@@ -12259,12 +12277,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12274,7 +12292,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12287,24 +12305,20 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H164" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr"/>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -12321,28 +12335,26 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E165" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v/>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
@@ -12361,16 +12373,20 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L165" s="12" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L165" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M165" s="12" t="inlineStr"/>
       <c r="N165" s="13" t="n">
         <v>0</v>
@@ -12385,28 +12401,26 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E166" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v/>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
@@ -12420,7 +12434,7 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
@@ -12432,7 +12446,7 @@
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12449,23 +12463,27 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C167" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -12485,14 +12503,14 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12509,21 +12527,29 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C168" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E168" s="15" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E168" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12531,35 +12557,31 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H168" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H168" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M168" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>8.75</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr"/>
+      <c r="M168" s="15" t="inlineStr"/>
       <c r="N168" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O168" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P168" s="16" t="n">
@@ -12569,21 +12591,25 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr"/>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12591,35 +12617,31 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H169" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M169" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr"/>
+      <c r="M169" s="12" t="inlineStr"/>
       <c r="N169" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O169" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P169" s="13" t="n">
@@ -12629,18 +12651,18 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr"/>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E170" s="15" t="inlineStr"/>
@@ -12651,27 +12673,35 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr"/>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr"/>
-      <c r="M170" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M170" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N170" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O170" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O170" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P170" s="16" t="n">
@@ -12681,18 +12711,18 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr"/>
@@ -12703,27 +12733,35 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr"/>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr"/>
-      <c r="M171" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N171" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O171" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O171" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P171" s="13" t="n">
@@ -12733,18 +12771,18 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr"/>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr"/>
@@ -12761,11 +12799,11 @@
       <c r="H172" s="15" t="inlineStr"/>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K172" s="15" t="n">
         <v>0.5</v>
@@ -12783,31 +12821,135 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="18" t="inlineStr">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1021</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr"/>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr"/>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr"/>
+      <c r="I173" s="12" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J173" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K173" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr"/>
+      <c r="M173" s="12" t="inlineStr"/>
+      <c r="N173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="14" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B174" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr"/>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="inlineStr"/>
+      <c r="F174" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G174" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="inlineStr"/>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J174" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K174" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L174" s="15" t="inlineStr"/>
+      <c r="M174" s="15" t="inlineStr"/>
+      <c r="N174" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B173" s="18" t="inlineStr"/>
-      <c r="C173" s="18" t="inlineStr"/>
-      <c r="D173" s="18" t="inlineStr"/>
-      <c r="E173" s="18" t="inlineStr"/>
-      <c r="F173" s="18" t="inlineStr"/>
-      <c r="G173" s="18" t="inlineStr"/>
-      <c r="H173" s="18" t="inlineStr"/>
-      <c r="I173" s="18" t="inlineStr"/>
-      <c r="J173" s="18" t="inlineStr"/>
-      <c r="K173" s="18" t="inlineStr"/>
-      <c r="L173" s="18" t="inlineStr"/>
-      <c r="M173" s="18" t="inlineStr"/>
-      <c r="N173" s="19" t="n">
-        <v>70876.86000000002</v>
-      </c>
-      <c r="O173" s="19" t="n">
-        <v>22553.97</v>
-      </c>
-      <c r="P173" s="19" t="n">
-        <v>114.5</v>
+      <c r="B175" s="18" t="inlineStr"/>
+      <c r="C175" s="18" t="inlineStr"/>
+      <c r="D175" s="18" t="inlineStr"/>
+      <c r="E175" s="18" t="inlineStr"/>
+      <c r="F175" s="18" t="inlineStr"/>
+      <c r="G175" s="18" t="inlineStr"/>
+      <c r="H175" s="18" t="inlineStr"/>
+      <c r="I175" s="18" t="inlineStr"/>
+      <c r="J175" s="18" t="inlineStr"/>
+      <c r="K175" s="18" t="inlineStr"/>
+      <c r="L175" s="18" t="inlineStr"/>
+      <c r="M175" s="18" t="inlineStr"/>
+      <c r="N175" s="19" t="n">
+        <v>70876.86</v>
+      </c>
+      <c r="O175" s="19" t="n">
+        <v>22947.97</v>
+      </c>
+      <c r="P175" s="19" t="n">
+        <v>115.33</v>
       </c>
     </row>
   </sheetData>
@@ -12981,6 +13123,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13555,7 +13699,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>30.75</v>
@@ -13564,7 +13708,7 @@
         <v>2.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>137.5</v>
+        <v>139.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>34.5</v>
@@ -13574,7 +13718,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13760,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>70.33</v>
+        <v>71.33</v>
       </c>
     </row>
   </sheetData>
@@ -13701,10 +13845,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>401279</v>
+        <v>400885</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>206569</v>
+        <v>206175</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>194710</v>
@@ -13751,10 +13895,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>214886</v>
+        <v>214492</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>126523</v>
+        <v>126129</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>88363</v>
@@ -13780,7 +13924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13804,7 +13948,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 7 commande(s)</t>
+          <t>Épics créées ce mois — 8 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13859,22 +14003,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -13884,7 +14028,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -13894,32 +14038,32 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -13939,32 +14083,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -13974,7 +14118,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -13984,22 +14128,22 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -14009,7 +14153,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14029,32 +14173,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>4475</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14074,32 +14218,32 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>2035</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -14109,7 +14253,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -14119,83 +14263,107 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I12" s="27" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>7 commande(s)</t>
-        </is>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>13610</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B13" s="18" t="n"/>
@@ -14206,17 +14374,17 @@
       <c r="G13" s="18" t="n"/>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>8 commande(s)</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>4300</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
@@ -14227,10 +14395,31 @@
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I14" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>7 commande(s)</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="n">
         <v>9310</v>
       </c>
     </row>
@@ -14245,7 +14434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -14266,7 +14455,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
+          <t>7 clôture(s) : 7 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -14366,22 +14555,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLA</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14390,28 +14579,28 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14420,65 +14609,125 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-21544</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>LA CIOTAT</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31947</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-33720</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n">
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-07-15.xlsx
+++ b/jira_export_2026-07-15.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>321 h</t>
+          <t>322 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>22947.97</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>115.33</v>
+        <v>115.04</v>
       </c>
     </row>
   </sheetData>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5.75</v>
@@ -13738,7 +13738,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>57.75</v>
+        <v>58.25</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>13</v>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-07-15.xlsx
+++ b/jira_export_2026-07-15.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>322 h</t>
+          <t>327 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>22947.97</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>115.04</v>
+        <v>114.75</v>
       </c>
     </row>
   </sheetData>
@@ -13711,7 +13711,7 @@
         <v>139.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5.75</v>
@@ -13738,7 +13738,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>58.25</v>
+        <v>58.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>13</v>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -13760,7 +13760,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>71.33</v>
+        <v>74.33</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-15.xlsx
+++ b/jira_export_2026-07-15.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>22,948 €</t>
+          <t>26,600 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>16,931 €</t>
+          <t>20,583 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -3190,10 +3190,10 @@
         <v>1365</v>
       </c>
       <c r="O34" s="17" t="n">
-        <v>0</v>
+        <v>1189.5</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0</v>
+        <v>1189.5</v>
       </c>
     </row>
     <row r="35">
@@ -3622,10 +3622,10 @@
         <v>407</v>
       </c>
       <c r="O40" s="17" t="n">
-        <v>0</v>
+        <v>203.5</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0</v>
+        <v>135.67</v>
       </c>
     </row>
     <row r="41">
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>0</v>
+        <v>732.6</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="45">
@@ -4910,10 +4910,10 @@
         <v>1618.5</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>1618.5</v>
+        <v>1942.2</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>431.6</v>
+        <v>517.92</v>
       </c>
     </row>
     <row r="59">
@@ -6277,11 +6277,11 @@
       <c r="N77" s="13" t="n">
         <v>765</v>
       </c>
-      <c r="O77" s="17" t="n">
-        <v>0</v>
+      <c r="O77" s="13" t="n">
+        <v>892.5</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>274.62</v>
       </c>
     </row>
     <row r="78">
@@ -6350,10 +6350,10 @@
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79">
@@ -6926,10 +6926,10 @@
         <v>420</v>
       </c>
       <c r="O86" s="17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87">
@@ -12946,10 +12946,10 @@
         <v>70876.86</v>
       </c>
       <c r="O175" s="19" t="n">
-        <v>22947.97</v>
+        <v>26599.77</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>114.75</v>
+        <v>133.01</v>
       </c>
     </row>
   </sheetData>
@@ -13845,16 +13845,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>400885</v>
+        <v>397233</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>206175</v>
+        <v>205338</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>194710</v>
+        <v>191895</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>157404</v>
+        <v>154589</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -13895,16 +13895,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>214492</v>
+        <v>210840</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>126129</v>
+        <v>125292</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>88363</v>
+        <v>85548</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>65355</v>
+        <v>62540</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>11857</v>
